--- a/РАБОЧИЙ СТОЛ/машины ПОКОМ ЗПФ.xlsx
+++ b/РАБОЧИЙ СТОЛ/машины ПОКОМ ЗПФ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28ECB9C4-9E09-40DD-B16C-E485F843DAA9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54525BBB-6F46-4420-B978-143165D5822F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>Бердянск</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Горняк Луганск</t>
+  </si>
+  <si>
+    <t>Мариуполь</t>
   </si>
 </sst>
 </file>
@@ -956,7 +959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -1073,11 +1076,11 @@
       <c r="J4" s="2"/>
       <c r="K4" s="7"/>
       <c r="L4" s="2">
-        <f t="shared" ref="L4:L11" si="0">B4-D4-F4-H4-J4</f>
+        <f t="shared" ref="L4:L12" si="0">B4-D4-F4-H4-J4</f>
         <v>0</v>
       </c>
       <c r="M4" s="3">
-        <f t="shared" ref="M4:M11" si="1">C4-E4-G4-I4-K4</f>
+        <f t="shared" ref="M4:M12" si="1">C4-E4-G4-I4-K4</f>
         <v>0</v>
       </c>
     </row>
@@ -1129,7 +1132,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="10"/>
@@ -1142,28 +1145,28 @@
       <c r="J7" s="2"/>
       <c r="K7" s="7"/>
       <c r="L7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="L7" si="2">B7-D7-F7-H7-J7</f>
         <v>0</v>
       </c>
       <c r="M7" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="M7" si="3">C7-E7-G7-I7-K7</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B8" s="17"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="12"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="7"/>
       <c r="L8" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1173,12 +1176,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="26"/>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="14"/>
       <c r="D9" s="11"/>
       <c r="E9" s="13"/>
       <c r="F9" s="11"/>
@@ -1187,94 +1190,117 @@
       <c r="I9" s="12"/>
       <c r="J9" s="11"/>
       <c r="K9" s="12"/>
-      <c r="L9" s="19">
+      <c r="L9" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M9" s="20">
+      <c r="M9" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
+    <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="25"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="21">
-        <f>SUM(B3:B9)</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="21">
-        <f>SUM(C3:C9)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="15">
-        <f>SUM(D3:D9)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="16">
-        <f t="shared" ref="E10:I10" si="2">SUM(E3:E9)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="16">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="16">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="15">
-        <f t="shared" ref="J10:K10" si="3">SUM(J3:J9)</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="28">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="29">
+      <c r="B11" s="21">
+        <f>SUM(B3:B10)</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="21">
+        <f>SUM(C3:C10)</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="15">
+        <f>SUM(D3:D10)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="16">
+        <f t="shared" ref="E11:I11" si="4">SUM(E3:E10)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="15">
+        <f t="shared" ref="J11:K11" si="5">SUM(J3:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M10" s="30">
+      <c r="M11" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="s">
+    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="32"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="35"/>
-      <c r="L11" s="36">
+      <c r="B12" s="32"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M11" s="37">
+      <c r="M12" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C12" s="27"/>
-      <c r="M12" s="27"/>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C13" s="27"/>
+      <c r="M13" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/РАБОЧИЙ СТОЛ/машины ПОКОМ ЗПФ.xlsx
+++ b/РАБОЧИЙ СТОЛ/машины ПОКОМ ЗПФ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54525BBB-6F46-4420-B978-143165D5822F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA27984-C17B-4EFB-A4FF-3C66986AB9D8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>Бердянск</t>
   </si>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t>нетто</t>
-  </si>
-  <si>
-    <t>Владстандарт</t>
   </si>
   <si>
     <t>ПРС ЛП</t>
@@ -124,7 +121,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -137,14 +134,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="34">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -534,34 +525,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
@@ -601,7 +564,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -630,16 +593,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -676,7 +632,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -959,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -975,68 +931,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="48" t="s">
+      <c r="C1" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="49"/>
-      <c r="F1" s="48" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="48" t="s">
+      <c r="G1" s="42"/>
+      <c r="H1" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="49"/>
-      <c r="J1" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="50"/>
-      <c r="L1" s="42" t="s">
+      <c r="I1" s="42"/>
+      <c r="J1" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="38" t="s">
-        <v>18</v>
+      <c r="K1" s="43"/>
+      <c r="L1" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="31" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="41"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="34"/>
       <c r="D2" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>10</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="43"/>
-      <c r="M2" s="39"/>
+        <v>16</v>
+      </c>
+      <c r="L2" s="36"/>
+      <c r="M2" s="32"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
@@ -1076,11 +1032,11 @@
       <c r="J4" s="2"/>
       <c r="K4" s="7"/>
       <c r="L4" s="2">
-        <f t="shared" ref="L4:L12" si="0">B4-D4-F4-H4-J4</f>
+        <f t="shared" ref="L4:L11" si="0">B4-D4-F4-H4-J4</f>
         <v>0</v>
       </c>
       <c r="M4" s="3">
-        <f t="shared" ref="M4:M12" si="1">C4-E4-G4-I4-K4</f>
+        <f t="shared" ref="M4:M11" si="1">C4-E4-G4-I4-K4</f>
         <v>0</v>
       </c>
     </row>
@@ -1132,7 +1088,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="10"/>
@@ -1155,7 +1111,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="10"/>
@@ -1178,7 +1134,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="14"/>
@@ -1201,7 +1157,7 @@
     </row>
     <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="25"/>
       <c r="C10" s="26"/>
@@ -1275,32 +1231,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="37">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C13" s="27"/>
-      <c r="M13" s="27"/>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C12" s="27"/>
+      <c r="M12" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="9">
